--- a/analytics/analytics.xlsx
+++ b/analytics/analytics.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Municipii'!$A$1:$AV$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Capitole'!$A$1:$J$446</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Capitole'!$A$1:$J$457</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Surse augmentare'!$A$1:$C$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -218,8 +218,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CapitoleAnalytics" displayName="CapitoleAnalytics" ref="A1:J446" headerRowCount="1">
-  <autoFilter ref="A1:J446"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CapitoleAnalytics" displayName="CapitoleAnalytics" ref="A1:J457" headerRowCount="1">
+  <autoFilter ref="A1:J457"/>
   <tableColumns count="10">
     <tableColumn id="1" name="An"/>
     <tableColumn id="2" name="SIRUTA"/>
@@ -635,7 +635,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>36.1</v>
       </c>
       <c r="AH9" s="9" t="n">
-        <v>42.31</v>
+        <v>-38.8</v>
       </c>
       <c r="AI9" s="9" t="n">
         <v>-16.85</v>
@@ -10906,8 +10906,12 @@
       <c r="AE62" s="8" t="n"/>
       <c r="AF62" s="9" t="n"/>
       <c r="AG62" s="9" t="n"/>
-      <c r="AH62" s="9" t="n"/>
-      <c r="AI62" s="9" t="n"/>
+      <c r="AH62" s="9" t="n">
+        <v>48.51</v>
+      </c>
+      <c r="AI62" s="9" t="n">
+        <v>37.79</v>
+      </c>
       <c r="AJ62" t="inlineStr">
         <is>
           <t>nu</t>
@@ -10961,8 +10965,12 @@
           <t>final</t>
         </is>
       </c>
-      <c r="AU62" s="9" t="n"/>
-      <c r="AV62" s="9" t="n"/>
+      <c r="AU62" s="9" t="n">
+        <v>39.05</v>
+      </c>
+      <c r="AV62" s="9" t="n">
+        <v>29.02</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11214,7 +11222,9 @@
       <c r="AF64" s="9" t="n"/>
       <c r="AG64" s="9" t="n"/>
       <c r="AH64" s="9" t="n"/>
-      <c r="AI64" s="9" t="n"/>
+      <c r="AI64" s="9" t="n">
+        <v>93.14</v>
+      </c>
       <c r="AJ64" t="inlineStr">
         <is>
           <t>nu</t>
@@ -11269,7 +11279,9 @@
         </is>
       </c>
       <c r="AU64" s="9" t="n"/>
-      <c r="AV64" s="9" t="n"/>
+      <c r="AV64" s="9" t="n">
+        <v>80.84</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -14322,7 +14334,7 @@
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>68.8</v>
+        <v>64</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -14520,10 +14532,10 @@
         <v/>
       </c>
       <c r="T85" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U85" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V85" s="8" t="n"/>
       <c r="X85" s="7" t="n"/>
@@ -14641,7 +14653,7 @@
         </is>
       </c>
       <c r="H86" s="5" t="n">
-        <v>58.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -14794,7 +14806,7 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -14839,10 +14851,10 @@
         <v/>
       </c>
       <c r="T87" s="8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U87" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V87" s="8" t="n"/>
       <c r="X87" s="7" t="n"/>
@@ -14998,10 +15010,10 @@
         <v/>
       </c>
       <c r="T88" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U88" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V88" s="8" t="n"/>
       <c r="X88" s="7" t="n"/>
@@ -15105,7 +15117,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>nu</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>total_cheltuieli_lipsa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -15114,7 +15131,7 @@
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>36.2</v>
+        <v>90.3</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -15137,11 +15154,9 @@
         <v/>
       </c>
       <c r="N89" s="7" t="n">
-        <v>586400</v>
-      </c>
-      <c r="O89" s="7" t="n">
-        <v>275840</v>
-      </c>
+        <v>311707</v>
+      </c>
+      <c r="O89" s="7" t="n"/>
       <c r="P89" s="7">
         <f>IF(OR($E89&lt;&gt;"da",N89="",O89=""),"",N89-O89)</f>
         <v/>
@@ -15158,12 +15173,8 @@
         <f>IF(OR($E89&lt;&gt;"da",P89=""),"",IFERROR(P89*1000/J89,""))</f>
         <v/>
       </c>
-      <c r="T89" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v>24</v>
-      </c>
+      <c r="T89" s="8" t="n"/>
+      <c r="U89" s="8" t="n"/>
       <c r="V89" s="8" t="n"/>
       <c r="X89" s="7" t="n"/>
       <c r="Y89" s="7" t="n"/>
@@ -15275,7 +15286,7 @@
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>78.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -15318,10 +15329,10 @@
         <v/>
       </c>
       <c r="T90" s="8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U90" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V90" s="8" t="n"/>
       <c r="X90" s="7" t="n"/>
@@ -15434,7 +15445,7 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>89.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -15457,7 +15468,7 @@
         <v/>
       </c>
       <c r="N91" s="7" t="n">
-        <v>707391.1</v>
+        <v>1645039.04</v>
       </c>
       <c r="O91" s="7" t="n">
         <v>1923999.23</v>
@@ -15479,10 +15490,10 @@
         <v/>
       </c>
       <c r="T91" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U91" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V91" s="8" t="n"/>
       <c r="X91" s="7" t="n"/>
@@ -15595,7 +15606,7 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -15643,7 +15654,7 @@
         <v>16</v>
       </c>
       <c r="U92" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V92" s="8" t="n"/>
       <c r="X92" s="7" t="n"/>
@@ -15756,7 +15767,7 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>58.3</v>
+        <v>54.4</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -15799,10 +15810,10 @@
         <v/>
       </c>
       <c r="T93" s="8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U93" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V93" s="8" t="n"/>
       <c r="X93" s="7" t="n"/>
@@ -15958,10 +15969,10 @@
         <v/>
       </c>
       <c r="T94" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U94" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V94" s="8" t="n"/>
       <c r="X94" s="7" t="n"/>
@@ -16079,7 +16090,7 @@
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>53.1</v>
+        <v>42.6</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -16234,7 +16245,7 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>84.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -16260,7 +16271,7 @@
         <v>2563356.898</v>
       </c>
       <c r="O96" s="7" t="n">
-        <v>2996612.8</v>
+        <v>1332108.8</v>
       </c>
       <c r="P96" s="7">
         <f>IF(OR($E96&lt;&gt;"da",N96="",O96=""),"",N96-O96)</f>
@@ -16279,10 +16290,10 @@
         <v/>
       </c>
       <c r="T96" s="8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="U96" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V96" s="8" t="n"/>
       <c r="X96" s="7" t="n"/>
@@ -16395,7 +16406,7 @@
         </is>
       </c>
       <c r="H97" s="5" t="n">
-        <v>75.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -16440,10 +16451,10 @@
         <v/>
       </c>
       <c r="T97" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U97" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V97" s="8" t="n"/>
       <c r="X97" s="7" t="n"/>
@@ -16561,7 +16572,7 @@
         </is>
       </c>
       <c r="H98" s="5" t="n">
-        <v>92.3</v>
+        <v>91.8</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -16759,10 +16770,10 @@
         <v/>
       </c>
       <c r="T99" s="8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U99" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V99" s="8" t="n"/>
       <c r="X99" s="7" t="n"/>
@@ -16923,7 +16934,7 @@
         <v>18</v>
       </c>
       <c r="U100" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V100" s="8" t="n"/>
       <c r="X100" s="7" t="n"/>
@@ -17036,7 +17047,7 @@
         </is>
       </c>
       <c r="H101" s="5" t="n">
-        <v>88.2</v>
+        <v>63.3</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -17058,7 +17069,9 @@
         <f>IFERROR(J101/L101,"")</f>
         <v/>
       </c>
-      <c r="N101" s="7" t="n"/>
+      <c r="N101" s="7" t="n">
+        <v>524948</v>
+      </c>
       <c r="O101" s="7" t="n">
         <v>399391.3</v>
       </c>
@@ -17079,10 +17092,10 @@
         <v/>
       </c>
       <c r="T101" s="8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="U101" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V101" s="8" t="n"/>
       <c r="X101" s="7" t="n"/>
@@ -17200,7 +17213,7 @@
         </is>
       </c>
       <c r="H102" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -17344,12 +17357,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>total_cheltuieli_lipsa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -17358,7 +17366,7 @@
         </is>
       </c>
       <c r="H103" s="5" t="n">
-        <v>83</v>
+        <v>58.2</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -17383,7 +17391,9 @@
       <c r="N103" s="7" t="n">
         <v>283422.01</v>
       </c>
-      <c r="O103" s="7" t="n"/>
+      <c r="O103" s="7" t="n">
+        <v>342425.31</v>
+      </c>
       <c r="P103" s="7">
         <f>IF(OR($E103&lt;&gt;"da",N103="",O103=""),"",N103-O103)</f>
         <v/>
@@ -17400,8 +17410,12 @@
         <f>IF(OR($E103&lt;&gt;"da",P103=""),"",IFERROR(P103*1000/J103,""))</f>
         <v/>
       </c>
-      <c r="T103" s="8" t="n"/>
-      <c r="U103" s="8" t="n"/>
+      <c r="T103" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U103" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="V103" s="8" t="n"/>
       <c r="X103" s="7" t="n"/>
       <c r="Y103" s="7" t="n"/>
@@ -17504,7 +17518,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>nu</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>total_cheltuieli_lipsa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -17513,7 +17532,7 @@
         </is>
       </c>
       <c r="H104" s="5" t="n">
-        <v>86.5</v>
+        <v>82.2</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -17538,9 +17557,7 @@
       <c r="N104" s="7" t="n">
         <v>344442.03</v>
       </c>
-      <c r="O104" s="7" t="n">
-        <v>365412.8</v>
-      </c>
+      <c r="O104" s="7" t="n"/>
       <c r="P104" s="7">
         <f>IF(OR($E104&lt;&gt;"da",N104="",O104=""),"",N104-O104)</f>
         <v/>
@@ -17557,12 +17574,8 @@
         <f>IF(OR($E104&lt;&gt;"da",P104=""),"",IFERROR(P104*1000/J104,""))</f>
         <v/>
       </c>
-      <c r="T104" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U104" s="8" t="n">
-        <v>24</v>
-      </c>
+      <c r="T104" s="8" t="n"/>
+      <c r="U104" s="8" t="n"/>
       <c r="V104" s="8" t="n"/>
       <c r="X104" s="7" t="n"/>
       <c r="Y104" s="7" t="n"/>
@@ -17665,12 +17678,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>total_cheltuieli_lipsa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -17679,7 +17687,7 @@
         </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>47.9</v>
+        <v>52.6</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -17701,10 +17709,10 @@
         <f>IFERROR(J105/L105,"")</f>
         <v/>
       </c>
-      <c r="N105" s="7" t="n">
-        <v>430467.31</v>
-      </c>
-      <c r="O105" s="7" t="n"/>
+      <c r="N105" s="7" t="n"/>
+      <c r="O105" s="7" t="n">
+        <v>253812.23</v>
+      </c>
       <c r="P105" s="7">
         <f>IF(OR($E105&lt;&gt;"da",N105="",O105=""),"",N105-O105)</f>
         <v/>
@@ -17721,8 +17729,12 @@
         <f>IF(OR($E105&lt;&gt;"da",P105=""),"",IFERROR(P105*1000/J105,""))</f>
         <v/>
       </c>
-      <c r="T105" s="8" t="n"/>
-      <c r="U105" s="8" t="n"/>
+      <c r="T105" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="U105" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="V105" s="8" t="n"/>
       <c r="X105" s="7" t="n"/>
       <c r="Y105" s="7" t="n"/>
@@ -17882,7 +17894,7 @@
         <v>17</v>
       </c>
       <c r="U106" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V106" s="8" t="n"/>
       <c r="X106" s="7" t="n"/>
@@ -17986,12 +17998,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>total_cheltuieli_lipsa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -18000,7 +18007,7 @@
         </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>94.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -18025,7 +18032,9 @@
       <c r="N107" s="7" t="n">
         <v>1729806.14</v>
       </c>
-      <c r="O107" s="7" t="n"/>
+      <c r="O107" s="7" t="n">
+        <v>1747515.15</v>
+      </c>
       <c r="P107" s="7">
         <f>IF(OR($E107&lt;&gt;"da",N107="",O107=""),"",N107-O107)</f>
         <v/>
@@ -18042,8 +18051,12 @@
         <f>IF(OR($E107&lt;&gt;"da",P107=""),"",IFERROR(P107*1000/J107,""))</f>
         <v/>
       </c>
-      <c r="T107" s="8" t="n"/>
-      <c r="U107" s="8" t="n"/>
+      <c r="T107" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="U107" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="V107" s="8" t="n"/>
       <c r="X107" s="7" t="n"/>
       <c r="Y107" s="7" t="n"/>
@@ -18200,10 +18213,10 @@
         <v/>
       </c>
       <c r="T108" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U108" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V108" s="8" t="n"/>
       <c r="X108" s="7" t="n"/>
@@ -18467,7 +18480,7 @@
         </is>
       </c>
       <c r="H110" s="5" t="n">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -18622,7 +18635,7 @@
         </is>
       </c>
       <c r="H111" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -18667,10 +18680,10 @@
         <v/>
       </c>
       <c r="T111" s="8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U111" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V111" s="8" t="n"/>
       <c r="X111" s="7" t="n"/>
@@ -18788,7 +18801,7 @@
         </is>
       </c>
       <c r="H112" s="5" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -18946,7 +18959,7 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>92.59999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -19147,7 +19160,7 @@
         <v>15</v>
       </c>
       <c r="U114" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V114" s="8" t="n"/>
       <c r="X114" s="7" t="n"/>
@@ -19265,7 +19278,7 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>40.3</v>
+        <v>57.5</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -19287,7 +19300,9 @@
         <f>IFERROR(J115/L115,"")</f>
         <v/>
       </c>
-      <c r="N115" s="7" t="n"/>
+      <c r="N115" s="7" t="n">
+        <v>382743.76</v>
+      </c>
       <c r="O115" s="7" t="n"/>
       <c r="P115" s="7">
         <f>IF(OR($E115&lt;&gt;"da",N115="",O115=""),"",N115-O115)</f>
@@ -19423,7 +19438,7 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>57.6</v>
+        <v>48</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -19569,12 +19584,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>total_cheltuieli_lipsa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -19583,7 +19593,7 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -19608,7 +19618,9 @@
       <c r="N117" s="7" t="n">
         <v>1069340.06</v>
       </c>
-      <c r="O117" s="7" t="n"/>
+      <c r="O117" s="7" t="n">
+        <v>1069740.09</v>
+      </c>
       <c r="P117" s="7">
         <f>IF(OR($E117&lt;&gt;"da",N117="",O117=""),"",N117-O117)</f>
         <v/>
@@ -19625,8 +19637,12 @@
         <f>IF(OR($E117&lt;&gt;"da",P117=""),"",IFERROR(P117*1000/J117,""))</f>
         <v/>
       </c>
-      <c r="T117" s="8" t="n"/>
-      <c r="U117" s="8" t="n"/>
+      <c r="T117" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="V117" s="8" t="n"/>
       <c r="X117" s="7" t="n"/>
       <c r="Y117" s="7" t="n"/>
@@ -19781,10 +19797,10 @@
         <v/>
       </c>
       <c r="T118" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U118" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V118" s="8" t="n"/>
       <c r="X118" s="7" t="n"/>
@@ -19942,10 +19958,10 @@
         <v/>
       </c>
       <c r="T119" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U119" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V119" s="8" t="n"/>
       <c r="X119" s="7" t="n"/>
@@ -20058,7 +20074,7 @@
         </is>
       </c>
       <c r="H120" s="5" t="n">
-        <v>81.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -20103,10 +20119,10 @@
         <v/>
       </c>
       <c r="T120" s="8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="U120" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V120" s="8" t="n"/>
       <c r="X120" s="7" t="n"/>
@@ -20219,7 +20235,7 @@
         </is>
       </c>
       <c r="H121" s="5" t="n">
-        <v>50.4</v>
+        <v>61.1</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -20264,10 +20280,10 @@
         <v/>
       </c>
       <c r="T121" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U121" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V121" s="8" t="n"/>
       <c r="X121" s="7" t="n"/>
@@ -20385,7 +20401,7 @@
         </is>
       </c>
       <c r="H122" s="5" t="n">
-        <v>87</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -20531,12 +20547,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>nu</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>total_cheltuieli_lipsa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -20545,7 +20556,7 @@
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>70.3</v>
+        <v>58.8</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -20568,7 +20579,9 @@
         <v/>
       </c>
       <c r="N123" s="7" t="n"/>
-      <c r="O123" s="7" t="n"/>
+      <c r="O123" s="7" t="n">
+        <v>1756</v>
+      </c>
       <c r="P123" s="7">
         <f>IF(OR($E123&lt;&gt;"da",N123="",O123=""),"",N123-O123)</f>
         <v/>
@@ -20585,8 +20598,12 @@
         <f>IF(OR($E123&lt;&gt;"da",P123=""),"",IFERROR(P123*1000/J123,""))</f>
         <v/>
       </c>
-      <c r="T123" s="8" t="n"/>
-      <c r="U123" s="8" t="n"/>
+      <c r="T123" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="U123" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="V123" s="8" t="n"/>
       <c r="X123" s="7" t="n"/>
       <c r="Y123" s="7" t="n"/>
@@ -20743,10 +20760,10 @@
         <v/>
       </c>
       <c r="T124" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="U124" s="8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V124" s="8" t="n"/>
       <c r="X124" s="7" t="n"/>
@@ -20844,7 +20861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J446"/>
+  <dimension ref="A1:J457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -31914,37 +31931,37 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Locuínte, servicii si dezvoltare publica</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>188462</v>
+        <v>42409.93</v>
       </c>
       <c r="H252" t="n">
-        <v>68.31999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="I252" t="n">
-        <v>2389.32</v>
+        <v>471.17</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -31958,37 +31975,37 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>112497</v>
+        <v>42223.27</v>
       </c>
       <c r="H253" t="n">
-        <v>40.78</v>
+        <v>13.49</v>
       </c>
       <c r="I253" t="n">
-        <v>1426.23</v>
+        <v>469.1</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -32002,17 +32019,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -32026,13 +32043,13 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>109620</v>
+        <v>29042.71</v>
       </c>
       <c r="H254" t="n">
-        <v>39.74</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="I254" t="n">
-        <v>1389.76</v>
+        <v>322.66</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -32046,37 +32063,37 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Combustibili şi energie</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>46240</v>
+        <v>10000</v>
       </c>
       <c r="H255" t="n">
-        <v>16.76</v>
+        <v>3.2</v>
       </c>
       <c r="I255" t="n">
-        <v>586.23</v>
+        <v>111.1</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -32090,37 +32107,37 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>Sanatate total capitol:</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>43740</v>
+        <v>9566.6</v>
       </c>
       <c r="H256" t="n">
-        <v>15.86</v>
+        <v>3.06</v>
       </c>
       <c r="I256" t="n">
-        <v>554.53</v>
+        <v>106.28</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -32134,37 +32151,37 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>00.12</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>C. VENITURI NEFISCALE</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>30788</v>
+        <v>5110</v>
       </c>
       <c r="H257" t="n">
-        <v>11.16</v>
+        <v>1.63</v>
       </c>
       <c r="I257" t="n">
-        <v>390.33</v>
+        <v>56.77</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -32178,37 +32195,37 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>00.14</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>C2. VANZARI DE BUNURI SI SERVICII</t>
+          <t>Alte servicii publice generale Din total capitol:</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>28729</v>
+        <v>4807.23</v>
       </c>
       <c r="H258" t="n">
-        <v>10.42</v>
+        <v>1.54</v>
       </c>
       <c r="I258" t="n">
-        <v>364.23</v>
+        <v>53.41</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -32222,37 +32239,37 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Botoșani</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>56.02</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Transferuri cu caracter general intre diferite niveluri ale administra</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>21319</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>270.28</v>
+        <v>0</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -32266,37 +32283,37 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>00.10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si împrumuturi</t>
+          <t>A4. IMPOZITE SI TAXE PE BUNURI SI SERVICII</t>
         </is>
       </c>
       <c r="G260" t="n">
-        <v>11500</v>
+        <v>227452.99</v>
       </c>
       <c r="H260" t="n">
-        <v>4.17</v>
+        <v>11.82</v>
       </c>
       <c r="I260" t="n">
-        <v>145.8</v>
+        <v>957.34</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -32310,37 +32327,37 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bistrița</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Bistrița-Năsăud</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>4085</v>
+        <v>117628.29</v>
       </c>
       <c r="H261" t="n">
-        <v>1.48</v>
+        <v>6.11</v>
       </c>
       <c r="I261" t="n">
-        <v>51.79</v>
+        <v>495.09</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -32354,37 +32371,37 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>42409.93</v>
+        <v>79891</v>
       </c>
       <c r="H262" t="n">
-        <v>13.55</v>
+        <v>4.15</v>
       </c>
       <c r="I262" t="n">
-        <v>471.17</v>
+        <v>336.26</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -32398,37 +32415,37 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>00.12</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>C. VENITURI NEFISCALE</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>42223.27</v>
+        <v>79129.06</v>
       </c>
       <c r="H263" t="n">
-        <v>13.49</v>
+        <v>4.11</v>
       </c>
       <c r="I263" t="n">
-        <v>469.1</v>
+        <v>333.05</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -32442,37 +32459,37 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G264" t="n">
-        <v>29042.71</v>
+        <v>67138</v>
       </c>
       <c r="H264" t="n">
-        <v>9.279999999999999</v>
+        <v>3.49</v>
       </c>
       <c r="I264" t="n">
-        <v>322.66</v>
+        <v>282.58</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -32486,37 +32503,37 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Combustibili şi energie</t>
+          <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>10000</v>
+        <v>61347.1</v>
       </c>
       <c r="H265" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="I265" t="n">
-        <v>111.1</v>
+        <v>258.21</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -32530,37 +32547,37 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>00.14</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sanatate total capitol:</t>
+          <t>C2. VANZARI DE BUNURI SI SERVICII</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>9566.6</v>
+        <v>42210.06</v>
       </c>
       <c r="H266" t="n">
-        <v>3.06</v>
+        <v>2.19</v>
       </c>
       <c r="I266" t="n">
-        <v>106.28</v>
+        <v>177.66</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -32574,37 +32591,37 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>5110</v>
+        <v>39390</v>
       </c>
       <c r="H267" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="I267" t="n">
-        <v>56.77</v>
+        <v>165.79</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -32618,37 +32635,37 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>00.13</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale Din total capitol:</t>
+          <t>C1. VENITURI DIN PROPRIETATE</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>4807.23</v>
+        <v>36919</v>
       </c>
       <c r="H268" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="I268" t="n">
-        <v>53.41</v>
+        <v>155.39</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -32662,37 +32679,37 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Botoșani</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>56.02</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Transferuri cu caracter general intre diferite niveluri ale administra</t>
+          <t>Alte actiuni economice</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>21231.88</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>89.36</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -32706,37 +32723,37 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>117628.29</v>
+        <v>310627.2</v>
       </c>
       <c r="H270" t="n">
-        <v>6.11</v>
+        <v>35.19</v>
       </c>
       <c r="I270" t="n">
-        <v>495.09</v>
+        <v>2008.11</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -32750,37 +32767,37 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Asigurări și asistenfá socială</t>
         </is>
       </c>
       <c r="G271" t="n">
-        <v>79891</v>
+        <v>140240.01</v>
       </c>
       <c r="H271" t="n">
-        <v>4.15</v>
+        <v>15.89</v>
       </c>
       <c r="I271" t="n">
-        <v>336.26</v>
+        <v>906.61</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -32794,37 +32811,37 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Invăjământ</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>67138</v>
+        <v>126338.41</v>
       </c>
       <c r="H272" t="n">
-        <v>3.49</v>
+        <v>14.31</v>
       </c>
       <c r="I272" t="n">
-        <v>282.58</v>
+        <v>816.74</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -32838,37 +32855,37 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Actiuni generale economice, comerciale si de munca</t>
+          <t>Locuinfe, servicii și dezvoltare publică</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>61347.1</v>
+        <v>72196.74000000001</v>
       </c>
       <c r="H273" t="n">
-        <v>3.19</v>
+        <v>8.18</v>
       </c>
       <c r="I273" t="n">
-        <v>258.21</v>
+        <v>466.73</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -32882,37 +32899,37 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>Autoritäfi publice și acțiuni externe</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>39390</v>
+        <v>64938.32</v>
       </c>
       <c r="H274" t="n">
-        <v>2.05</v>
+        <v>7.36</v>
       </c>
       <c r="I274" t="n">
-        <v>165.79</v>
+        <v>419.81</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -32926,37 +32943,37 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Alte actiuni economice</t>
+          <t>Protecfia mediului</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>21231.88</v>
+        <v>60212.2</v>
       </c>
       <c r="H275" t="n">
-        <v>1.1</v>
+        <v>6.82</v>
       </c>
       <c r="I275" t="n">
-        <v>89.36</v>
+        <v>389.25</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -32970,37 +32987,37 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>17297.49</v>
+        <v>51895.3</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9</v>
+        <v>5.88</v>
       </c>
       <c r="I276" t="n">
-        <v>72.8</v>
+        <v>335.49</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -33014,37 +33031,37 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Combustibili si energie</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G277" t="n">
-        <v>2000</v>
+        <v>22891</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1</v>
+        <v>2.59</v>
       </c>
       <c r="I277" t="n">
-        <v>8.42</v>
+        <v>147.98</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -33058,37 +33075,37 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>Ordine publică și siguramjă națională</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>1393</v>
+        <v>20120.73</v>
       </c>
       <c r="H278" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="I278" t="n">
-        <v>5.86</v>
+        <v>130.07</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -33102,37 +33119,37 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>40198</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Brăila</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Agricultura, silvicultura, piscicultura si vanatoare</t>
+          <t>Atte servicii publice generale</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>429</v>
+        <v>11434.35</v>
       </c>
       <c r="H279" t="n">
-        <v>0.02</v>
+        <v>1.3</v>
       </c>
       <c r="I279" t="n">
-        <v>1.81</v>
+        <v>73.92</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -33146,37 +33163,37 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>310627.2</v>
+        <v>883560</v>
       </c>
       <c r="H280" t="n">
-        <v>35.19</v>
+        <v>11.2</v>
       </c>
       <c r="I280" t="n">
-        <v>2008.11</v>
+        <v>514.61</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -33190,37 +33207,37 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Asigurări și asistenfá socială</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G281" t="n">
-        <v>140240.01</v>
+        <v>543549</v>
       </c>
       <c r="H281" t="n">
-        <v>15.89</v>
+        <v>6.89</v>
       </c>
       <c r="I281" t="n">
-        <v>906.61</v>
+        <v>316.58</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -33234,37 +33251,37 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Invăjământ</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G282" t="n">
-        <v>126338.41</v>
+        <v>293154</v>
       </c>
       <c r="H282" t="n">
-        <v>14.31</v>
+        <v>3.71</v>
       </c>
       <c r="I282" t="n">
-        <v>816.74</v>
+        <v>170.74</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -33278,37 +33295,37 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Locuinfe, servicii și dezvoltare publică</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G283" t="n">
-        <v>72196.74000000001</v>
+        <v>150549</v>
       </c>
       <c r="H283" t="n">
-        <v>8.18</v>
+        <v>1.91</v>
       </c>
       <c r="I283" t="n">
-        <v>466.73</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -33322,37 +33339,37 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Autoritäfi publice și acțiuni externe</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>64938.32</v>
+        <v>32762</v>
       </c>
       <c r="H284" t="n">
-        <v>7.36</v>
+        <v>0.42</v>
       </c>
       <c r="I284" t="n">
-        <v>419.81</v>
+        <v>19.08</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -33366,37 +33383,37 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>54.10</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Protecfia mediului</t>
+          <t>Servicii publice comunitare de evidenta a persoanelor</t>
         </is>
       </c>
       <c r="G285" t="n">
-        <v>60212.2</v>
+        <v>12619</v>
       </c>
       <c r="H285" t="n">
-        <v>6.82</v>
+        <v>0.16</v>
       </c>
       <c r="I285" t="n">
-        <v>389.25</v>
+        <v>7.35</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -33410,37 +33427,37 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Agricultura, silvicultura, piscicultura si vanatoare</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>51895.3</v>
+        <v>4506</v>
       </c>
       <c r="H286" t="n">
-        <v>5.88</v>
+        <v>0.06</v>
       </c>
       <c r="I286" t="n">
-        <v>335.49</v>
+        <v>2.62</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -33454,37 +33471,37 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Alte actiuni economice</t>
         </is>
       </c>
       <c r="G287" t="n">
-        <v>22891</v>
+        <v>500</v>
       </c>
       <c r="H287" t="n">
-        <v>2.59</v>
+        <v>0.01</v>
       </c>
       <c r="I287" t="n">
-        <v>147.98</v>
+        <v>0.29</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -33498,37 +33515,37 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>București</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>60.02</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Ordine publică și siguramjă națională</t>
+          <t>Aparare nationala</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>20120.73</v>
+        <v>482</v>
       </c>
       <c r="H288" t="n">
-        <v>2.28</v>
+        <v>0.01</v>
       </c>
       <c r="I288" t="n">
-        <v>130.07</v>
+        <v>0.28</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -33542,37 +33559,37 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Brăila</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Atte servicii publice generale</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G289" t="n">
-        <v>11434.35</v>
+        <v>70110</v>
       </c>
       <c r="H289" t="n">
-        <v>1.3</v>
+        <v>10.16</v>
       </c>
       <c r="I289" t="n">
-        <v>73.92</v>
+        <v>677.52</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -33586,37 +33603,37 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>883560</v>
+        <v>26670</v>
       </c>
       <c r="H290" t="n">
-        <v>11.2</v>
+        <v>3.87</v>
       </c>
       <c r="I290" t="n">
-        <v>514.61</v>
+        <v>257.73</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -33630,37 +33647,37 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G291" t="n">
-        <v>543549</v>
+        <v>15271</v>
       </c>
       <c r="H291" t="n">
-        <v>6.89</v>
+        <v>2.21</v>
       </c>
       <c r="I291" t="n">
-        <v>316.58</v>
+        <v>147.57</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -33674,17 +33691,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -33694,17 +33711,17 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>Tranzactii privind datoria publica si imprumuturi ()</t>
         </is>
       </c>
       <c r="G292" t="n">
-        <v>293154</v>
+        <v>9600</v>
       </c>
       <c r="H292" t="n">
-        <v>3.71</v>
+        <v>1.39</v>
       </c>
       <c r="I292" t="n">
-        <v>170.74</v>
+        <v>92.77</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -33718,37 +33735,37 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>44818</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Buzău</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
       <c r="G293" t="n">
-        <v>150549</v>
+        <v>715</v>
       </c>
       <c r="H293" t="n">
-        <v>1.91</v>
+        <v>0.1</v>
       </c>
       <c r="I293" t="n">
-        <v>87.68000000000001</v>
+        <v>6.91</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -33762,37 +33779,37 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
       <c r="G294" t="n">
-        <v>32762</v>
+        <v>485803.89</v>
       </c>
       <c r="H294" t="n">
-        <v>0.42</v>
+        <v>76.67</v>
       </c>
       <c r="I294" t="n">
-        <v>19.08</v>
+        <v>8319.559999999999</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -33806,37 +33823,37 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>54.10</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Servicii publice comunitare de evidenta a persoanelor</t>
+          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
         </is>
       </c>
       <c r="G295" t="n">
-        <v>12619</v>
+        <v>36786</v>
       </c>
       <c r="H295" t="n">
-        <v>0.16</v>
+        <v>5.81</v>
       </c>
       <c r="I295" t="n">
-        <v>7.35</v>
+        <v>629.97</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -33850,37 +33867,37 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Agricultura, silvicultura, piscicultura si vanatoare</t>
+          <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>4506</v>
+        <v>31727.87</v>
       </c>
       <c r="H296" t="n">
-        <v>0.06</v>
+        <v>5.01</v>
       </c>
       <c r="I296" t="n">
-        <v>2.62</v>
+        <v>543.35</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -33894,37 +33911,37 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Alte actiuni economice</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>500</v>
+        <v>22404.85</v>
       </c>
       <c r="H297" t="n">
-        <v>0.01</v>
+        <v>3.54</v>
       </c>
       <c r="I297" t="n">
-        <v>0.29</v>
+        <v>383.69</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -33938,37 +33955,37 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Aparare nationala</t>
+          <t>INVATAMANT</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>482</v>
+        <v>17550.7</v>
       </c>
       <c r="H298" t="n">
-        <v>0.01</v>
+        <v>2.77</v>
       </c>
       <c r="I298" t="n">
-        <v>0.28</v>
+        <v>300.56</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -33982,37 +33999,37 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>TRANSPORTURI</t>
         </is>
       </c>
       <c r="G299" t="n">
-        <v>70110</v>
+        <v>17179</v>
       </c>
       <c r="H299" t="n">
-        <v>10.16</v>
+        <v>2.71</v>
       </c>
       <c r="I299" t="n">
-        <v>677.52</v>
+        <v>294.2</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -34026,37 +34043,37 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>TRANZACTII PRIVIND DATORIA PUBLICA SI IMPRUMUTURI</t>
         </is>
       </c>
       <c r="G300" t="n">
-        <v>26670</v>
+        <v>6527.5</v>
       </c>
       <c r="H300" t="n">
-        <v>3.87</v>
+        <v>1.03</v>
       </c>
       <c r="I300" t="n">
-        <v>257.73</v>
+        <v>111.79</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -34070,37 +34087,37 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
       </c>
       <c r="G301" t="n">
-        <v>15271</v>
+        <v>5325</v>
       </c>
       <c r="H301" t="n">
-        <v>2.21</v>
+        <v>0.84</v>
       </c>
       <c r="I301" t="n">
-        <v>147.57</v>
+        <v>91.19</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -34114,37 +34131,37 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi ()</t>
+          <t>SANATATE</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>9600</v>
+        <v>4790</v>
       </c>
       <c r="H302" t="n">
-        <v>1.39</v>
+        <v>0.76</v>
       </c>
       <c r="I302" t="n">
-        <v>92.77</v>
+        <v>82.03</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -34158,37 +34175,37 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>50790</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Reșița</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Buzău</t>
+          <t>Caraș-Severin</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Actiuni generale economice, comerciale si de munca</t>
+          <t>PROTECTIA MEDIULUI</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>715</v>
+        <v>4501</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
       <c r="I303" t="n">
-        <v>6.91</v>
+        <v>77.08</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -34202,37 +34219,37 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>54975</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Cluj-Napoca</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Cluj</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
+          <t>Combustibili si energie</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>485803.89</v>
+        <v>73000000</v>
       </c>
       <c r="H304" t="n">
-        <v>76.67</v>
+        <v>5480.03</v>
       </c>
       <c r="I304" t="n">
-        <v>8319.559999999999</v>
+        <v>254712.18</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -34246,37 +34263,37 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>54975</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Cluj-Napoca</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Cluj</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>83.02</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
+          <t>Agricultura, silvicultura, piscicultura si vanatoare</t>
         </is>
       </c>
       <c r="G305" t="n">
-        <v>36786</v>
+        <v>300000</v>
       </c>
       <c r="H305" t="n">
-        <v>5.81</v>
+        <v>22.52</v>
       </c>
       <c r="I305" t="n">
-        <v>629.97</v>
+        <v>1046.76</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -34290,37 +34307,37 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
+          <t>Combustibili si energie Din total capitol:</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>31727.87</v>
+        <v>603962</v>
       </c>
       <c r="H306" t="n">
-        <v>5.01</v>
+        <v>26.34</v>
       </c>
       <c r="I306" t="n">
-        <v>543.35</v>
+        <v>2290.44</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -34334,37 +34351,37 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>CULTURA, RECREERE SI RELIGIE</t>
+          <t>Protectia mediului Din total capitol:</t>
         </is>
       </c>
       <c r="G307" t="n">
-        <v>22404.85</v>
+        <v>235409</v>
       </c>
       <c r="H307" t="n">
-        <v>3.54</v>
+        <v>10.27</v>
       </c>
       <c r="I307" t="n">
-        <v>383.69</v>
+        <v>892.76</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
@@ -34378,37 +34395,37 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>INVATAMANT</t>
+          <t>Locuinte, servicii si dezvoltare publica Din total capitol:</t>
         </is>
       </c>
       <c r="G308" t="n">
-        <v>17550.7</v>
+        <v>210151</v>
       </c>
       <c r="H308" t="n">
-        <v>2.77</v>
+        <v>9.17</v>
       </c>
       <c r="I308" t="n">
-        <v>300.56</v>
+        <v>796.97</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
@@ -34422,37 +34439,37 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>TRANSPORTURI</t>
+          <t>Autoritati publice si actiuni externe Din total capitol:</t>
         </is>
       </c>
       <c r="G309" t="n">
-        <v>17179</v>
+        <v>135622</v>
       </c>
       <c r="H309" t="n">
-        <v>2.71</v>
+        <v>5.92</v>
       </c>
       <c r="I309" t="n">
-        <v>294.2</v>
+        <v>514.33</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
@@ -34466,37 +34483,37 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>TRANZACTII PRIVIND DATORIA PUBLICA SI IMPRUMUTURI</t>
+          <t>Sanatate Din total capitol:</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>6527.5</v>
+        <v>94070</v>
       </c>
       <c r="H310" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="I310" t="n">
-        <v>111.79</v>
+        <v>356.75</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
@@ -34510,37 +34527,37 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
+          <t>Transporturi Din total capitol:</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>5325</v>
+        <v>87466</v>
       </c>
       <c r="H311" t="n">
-        <v>0.84</v>
+        <v>3.82</v>
       </c>
       <c r="I311" t="n">
-        <v>91.19</v>
+        <v>331.7</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
@@ -34554,37 +34571,37 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SANATATE</t>
+          <t>Ordine publica si siguranta nationala Din total capitol:</t>
         </is>
       </c>
       <c r="G312" t="n">
-        <v>4790</v>
+        <v>57895</v>
       </c>
       <c r="H312" t="n">
-        <v>0.76</v>
+        <v>2.53</v>
       </c>
       <c r="I312" t="n">
-        <v>82.03</v>
+        <v>219.56</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
@@ -34598,37 +34615,37 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>50790</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Reșița</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Caraș-Severin</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>PROTECTIA MEDIULUI</t>
+          <t>Tranzacții privind datoria publică și împrumuturi</t>
         </is>
       </c>
       <c r="G313" t="n">
-        <v>4501</v>
+        <v>16674</v>
       </c>
       <c r="H313" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I313" t="n">
-        <v>77.08</v>
+        <v>63.23</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -34642,37 +34659,37 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Alte actiuni economice Din total capitol:</t>
         </is>
       </c>
       <c r="G314" t="n">
-        <v>560975000</v>
+        <v>3859</v>
       </c>
       <c r="H314" t="n">
-        <v>18720.3</v>
+        <v>0.17</v>
       </c>
       <c r="I314" t="n">
-        <v>1957358.39</v>
+        <v>14.63</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
@@ -34686,37 +34703,37 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Constanța</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Combustibili si energie</t>
+          <t>Actiuni generale economice, comerciale si de munca Din total capitol:</t>
         </is>
       </c>
       <c r="G315" t="n">
-        <v>73000000</v>
+        <v>2043</v>
       </c>
       <c r="H315" t="n">
-        <v>2436.08</v>
+        <v>0.09</v>
       </c>
       <c r="I315" t="n">
-        <v>254712.18</v>
+        <v>7.75</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
@@ -34730,37 +34747,37 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G316" t="n">
-        <v>60881000</v>
+        <v>236981</v>
       </c>
       <c r="H316" t="n">
-        <v>2031.66</v>
+        <v>19.21</v>
       </c>
       <c r="I316" t="n">
-        <v>212426.46</v>
+        <v>1012.13</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
@@ -34774,37 +34791,37 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>34912000</v>
+        <v>177264</v>
       </c>
       <c r="H317" t="n">
-        <v>1165.05</v>
+        <v>14.37</v>
       </c>
       <c r="I317" t="n">
-        <v>121815.23</v>
+        <v>757.09</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
@@ -34818,37 +34835,37 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G318" t="n">
-        <v>14672000</v>
+        <v>156265</v>
       </c>
       <c r="H318" t="n">
-        <v>489.62</v>
+        <v>12.67</v>
       </c>
       <c r="I318" t="n">
-        <v>51193.66</v>
+        <v>667.4</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -34862,37 +34879,37 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>54975</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Cluj-Napoca</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>83.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Agricultura, silvicultura, piscicultura si vanatoare</t>
+          <t>Sanatate © INDSOFT-SICO - MUNICIPIUL CRAIOVA</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>300000</v>
+        <v>138102</v>
       </c>
       <c r="H319" t="n">
-        <v>10.01</v>
+        <v>11.19</v>
       </c>
       <c r="I319" t="n">
-        <v>1046.76</v>
+        <v>589.83</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
@@ -34906,37 +34923,37 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Combustibili si energie Din total capitol:</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>603962</v>
+        <v>127280</v>
       </c>
       <c r="H320" t="n">
-        <v>26.34</v>
+        <v>10.32</v>
       </c>
       <c r="I320" t="n">
-        <v>2290.44</v>
+        <v>543.61</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
@@ -34950,17 +34967,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -34970,17 +34987,17 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Protectia mediului Din total capitol:</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>235409</v>
+        <v>125705</v>
       </c>
       <c r="H321" t="n">
-        <v>10.27</v>
+        <v>10.19</v>
       </c>
       <c r="I321" t="n">
-        <v>892.76</v>
+        <v>536.88</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
@@ -34994,37 +35011,37 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica Din total capitol:</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>210151</v>
+        <v>101323</v>
       </c>
       <c r="H322" t="n">
-        <v>9.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I322" t="n">
-        <v>796.97</v>
+        <v>432.75</v>
       </c>
       <c r="J322" t="inlineStr">
         <is>
@@ -35038,37 +35055,37 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe Din total capitol:</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>135622</v>
+        <v>88721</v>
       </c>
       <c r="H323" t="n">
-        <v>5.92</v>
+        <v>7.19</v>
       </c>
       <c r="I323" t="n">
-        <v>514.33</v>
+        <v>378.92</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
@@ -35082,37 +35099,37 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Sanatate Din total capitol:</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>94070</v>
+        <v>34033</v>
       </c>
       <c r="H324" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="I324" t="n">
-        <v>356.75</v>
+        <v>145.35</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -35126,37 +35143,37 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>69900</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Craiova</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dolj</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Transporturi Din total capitol:</t>
+          <t>Combustibili si energie</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>87466</v>
+        <v>27694</v>
       </c>
       <c r="H325" t="n">
-        <v>3.82</v>
+        <v>2.24</v>
       </c>
       <c r="I325" t="n">
-        <v>331.7</v>
+        <v>118.28</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -35170,37 +35187,37 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala Din total capitol:</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>57895</v>
+        <v>132573.89</v>
       </c>
       <c r="H326" t="n">
-        <v>2.53</v>
+        <v>21.97</v>
       </c>
       <c r="I326" t="n">
-        <v>219.56</v>
+        <v>1979.75</v>
       </c>
       <c r="J326" t="inlineStr">
         <is>
@@ -35214,37 +35231,37 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Tranzacții privind datoria publică și împrumuturi</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>16674</v>
+        <v>125956</v>
       </c>
       <c r="H327" t="n">
-        <v>0.73</v>
+        <v>20.87</v>
       </c>
       <c r="I327" t="n">
-        <v>63.23</v>
+        <v>1880.92</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
@@ -35258,37 +35275,37 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Alte actiuni economice Din total capitol:</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>3859</v>
+        <v>125058</v>
       </c>
       <c r="H328" t="n">
-        <v>0.17</v>
+        <v>20.72</v>
       </c>
       <c r="I328" t="n">
-        <v>14.63</v>
+        <v>1867.51</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -35302,37 +35319,37 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Constanța</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>80.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Actiuni generale economice, comerciale si de munca Din total capitol:</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>2043</v>
+        <v>72021</v>
       </c>
       <c r="H329" t="n">
-        <v>0.09</v>
+        <v>11.93</v>
       </c>
       <c r="I329" t="n">
-        <v>7.75</v>
+        <v>1075.5</v>
       </c>
       <c r="J329" t="inlineStr">
         <is>
@@ -35346,37 +35363,37 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>236981</v>
+        <v>32392</v>
       </c>
       <c r="H330" t="n">
-        <v>19.21</v>
+        <v>5.37</v>
       </c>
       <c r="I330" t="n">
-        <v>1012.13</v>
+        <v>483.72</v>
       </c>
       <c r="J330" t="inlineStr">
         <is>
@@ -35390,37 +35407,37 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G331" t="n">
-        <v>177264</v>
+        <v>32107</v>
       </c>
       <c r="H331" t="n">
-        <v>14.37</v>
+        <v>5.32</v>
       </c>
       <c r="I331" t="n">
-        <v>757.09</v>
+        <v>479.46</v>
       </c>
       <c r="J331" t="inlineStr">
         <is>
@@ -35434,37 +35451,37 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>156265</v>
+        <v>30183</v>
       </c>
       <c r="H332" t="n">
-        <v>12.67</v>
+        <v>5</v>
       </c>
       <c r="I332" t="n">
-        <v>667.4</v>
+        <v>450.73</v>
       </c>
       <c r="J332" t="inlineStr">
         <is>
@@ -35478,37 +35495,37 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Sanatate © INDSOFT-SICO - MUNICIPIUL CRAIOVA</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>138102</v>
+        <v>24599</v>
       </c>
       <c r="H333" t="n">
-        <v>11.19</v>
+        <v>4.08</v>
       </c>
       <c r="I333" t="n">
-        <v>589.83</v>
+        <v>367.34</v>
       </c>
       <c r="J333" t="inlineStr">
         <is>
@@ -35522,37 +35539,37 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G334" t="n">
-        <v>127280</v>
+        <v>10900</v>
       </c>
       <c r="H334" t="n">
-        <v>10.32</v>
+        <v>1.81</v>
       </c>
       <c r="I334" t="n">
-        <v>543.61</v>
+        <v>162.77</v>
       </c>
       <c r="J334" t="inlineStr">
         <is>
@@ -35566,37 +35583,37 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Târgoviște</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>125705</v>
+        <v>9990</v>
       </c>
       <c r="H335" t="n">
-        <v>10.19</v>
+        <v>1.66</v>
       </c>
       <c r="I335" t="n">
-        <v>536.88</v>
+        <v>149.18</v>
       </c>
       <c r="J335" t="inlineStr">
         <is>
@@ -35610,37 +35627,37 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>101323</v>
+        <v>133400</v>
       </c>
       <c r="H336" t="n">
-        <v>8.210000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="I336" t="n">
-        <v>432.75</v>
+        <v>612.35</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
@@ -35654,37 +35671,37 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>88721</v>
+        <v>120430</v>
       </c>
       <c r="H337" t="n">
-        <v>7.19</v>
+        <v>30.15</v>
       </c>
       <c r="I337" t="n">
-        <v>378.92</v>
+        <v>552.8099999999999</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -35698,37 +35715,37 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>34033</v>
+        <v>74656</v>
       </c>
       <c r="H338" t="n">
-        <v>2.76</v>
+        <v>18.69</v>
       </c>
       <c r="I338" t="n">
-        <v>145.35</v>
+        <v>342.69</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
@@ -35742,37 +35759,37 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>69900</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Craiova</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Dolj</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>74.10</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Combustibili si energie</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G339" t="n">
-        <v>27694</v>
+        <v>64985.3</v>
       </c>
       <c r="H339" t="n">
-        <v>2.24</v>
+        <v>16.27</v>
       </c>
       <c r="I339" t="n">
-        <v>118.28</v>
+        <v>298.3</v>
       </c>
       <c r="J339" t="inlineStr">
         <is>
@@ -35786,37 +35803,37 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>132573.89</v>
+        <v>52282</v>
       </c>
       <c r="H340" t="n">
-        <v>21.97</v>
+        <v>13.09</v>
       </c>
       <c r="I340" t="n">
-        <v>1979.75</v>
+        <v>239.99</v>
       </c>
       <c r="J340" t="inlineStr">
         <is>
@@ -35830,37 +35847,37 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>125956</v>
+        <v>42194</v>
       </c>
       <c r="H341" t="n">
-        <v>20.87</v>
+        <v>10.56</v>
       </c>
       <c r="I341" t="n">
-        <v>1880.92</v>
+        <v>193.68</v>
       </c>
       <c r="J341" t="inlineStr">
         <is>
@@ -35874,37 +35891,37 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>125058</v>
+        <v>40500</v>
       </c>
       <c r="H342" t="n">
-        <v>20.72</v>
+        <v>10.14</v>
       </c>
       <c r="I342" t="n">
-        <v>1867.51</v>
+        <v>185.91</v>
       </c>
       <c r="J342" t="inlineStr">
         <is>
@@ -35918,37 +35935,37 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>72021</v>
+        <v>25930</v>
       </c>
       <c r="H343" t="n">
-        <v>11.93</v>
+        <v>6.49</v>
       </c>
       <c r="I343" t="n">
-        <v>1075.5</v>
+        <v>119.03</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -35962,37 +35979,37 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>61.10</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>32392</v>
+        <v>25001</v>
       </c>
       <c r="H344" t="n">
-        <v>5.37</v>
+        <v>6.26</v>
       </c>
       <c r="I344" t="n">
-        <v>483.72</v>
+        <v>114.76</v>
       </c>
       <c r="J344" t="inlineStr">
         <is>
@@ -36006,37 +36023,37 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Galați</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>32107</v>
+        <v>22900</v>
       </c>
       <c r="H345" t="n">
-        <v>5.32</v>
+        <v>5.73</v>
       </c>
       <c r="I345" t="n">
-        <v>479.46</v>
+        <v>105.12</v>
       </c>
       <c r="J345" t="inlineStr">
         <is>
@@ -36050,37 +36067,37 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>30183</v>
+        <v>169034.16</v>
       </c>
       <c r="H346" t="n">
-        <v>5</v>
+        <v>49.36</v>
       </c>
       <c r="I346" t="n">
-        <v>450.73</v>
+        <v>2298.38</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -36094,37 +36111,37 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>INVATAMANT</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>24599</v>
+        <v>117436.03</v>
       </c>
       <c r="H347" t="n">
-        <v>4.08</v>
+        <v>34.3</v>
       </c>
       <c r="I347" t="n">
-        <v>367.34</v>
+        <v>1596.79</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -36138,37 +36155,37 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>AUTORITATI PUBLICE SI ACTIUNIEXTERNE</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>10900</v>
+        <v>52514.45</v>
       </c>
       <c r="H348" t="n">
-        <v>1.81</v>
+        <v>15.34</v>
       </c>
       <c r="I348" t="n">
-        <v>162.77</v>
+        <v>714.05</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -36182,37 +36199,37 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Târgoviște</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>9990</v>
+        <v>50184.42</v>
       </c>
       <c r="H349" t="n">
-        <v>1.66</v>
+        <v>14.66</v>
       </c>
       <c r="I349" t="n">
-        <v>149.18</v>
+        <v>682.36</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -36226,17 +36243,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -36246,17 +36263,17 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>74656</v>
+        <v>47252.64</v>
       </c>
       <c r="H350" t="n">
-        <v>18.69</v>
+        <v>13.8</v>
       </c>
       <c r="I350" t="n">
-        <v>342.69</v>
+        <v>642.5</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -36270,37 +36287,37 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>TRANSPORTUR1</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>70740</v>
+        <v>38153.55</v>
       </c>
       <c r="H351" t="n">
-        <v>17.71</v>
+        <v>11.14</v>
       </c>
       <c r="I351" t="n">
-        <v>324.72</v>
+        <v>518.78</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -36314,37 +36331,37 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>74.10</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>64985.3</v>
+        <v>22912.63</v>
       </c>
       <c r="H352" t="n">
-        <v>16.27</v>
+        <v>6.69</v>
       </c>
       <c r="I352" t="n">
-        <v>298.3</v>
+        <v>311.55</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -36358,37 +36375,37 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>PROTECTIA MEDIULU]</t>
         </is>
       </c>
       <c r="G353" t="n">
-        <v>52282</v>
+        <v>20967.39</v>
       </c>
       <c r="H353" t="n">
-        <v>13.09</v>
+        <v>6.12</v>
       </c>
       <c r="I353" t="n">
-        <v>239.99</v>
+        <v>285.1</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -36402,37 +36419,37 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Tranzactii privind datoria publica si imprumuturi</t>
+          <t>ORDINEPUBLICASISIGURANTA NATIOSALA</t>
         </is>
       </c>
       <c r="G354" t="n">
-        <v>40500</v>
+        <v>19334.64</v>
       </c>
       <c r="H354" t="n">
-        <v>10.14</v>
+        <v>5.65</v>
       </c>
       <c r="I354" t="n">
-        <v>185.91</v>
+        <v>262.9</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -36446,37 +36463,37 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>77812</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Târgu Jiu</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Gorj</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>ALTE SERVICII PUBLICE GENERALE</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>25930</v>
+        <v>4464.27</v>
       </c>
       <c r="H355" t="n">
-        <v>6.49</v>
+        <v>1.3</v>
       </c>
       <c r="I355" t="n">
-        <v>119.03</v>
+        <v>60.7</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -36490,37 +36507,37 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>61.10</t>
+          <t>00.10</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>A4. IMPOZITE SI TAXE PE BUNURI SI SERVICII</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>25001</v>
+        <v>120421.14</v>
       </c>
       <c r="H356" t="n">
-        <v>6.26</v>
+        <v>47.44</v>
       </c>
       <c r="I356" t="n">
-        <v>114.76</v>
+        <v>2267.26</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -36534,37 +36551,37 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>84.10</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>13461.13</v>
+        <v>67559.97</v>
       </c>
       <c r="H357" t="n">
-        <v>3.37</v>
+        <v>26.62</v>
       </c>
       <c r="I357" t="n">
-        <v>61.79</v>
+        <v>1272</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
@@ -36578,37 +36595,37 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>8379.870000000001</v>
+        <v>57786</v>
       </c>
       <c r="H358" t="n">
-        <v>2.1</v>
+        <v>22.77</v>
       </c>
       <c r="I358" t="n">
-        <v>38.47</v>
+        <v>1087.98</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -36622,37 +36639,37 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Galați</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
         </is>
       </c>
       <c r="G359" t="n">
-        <v>7600</v>
+        <v>43369.92</v>
       </c>
       <c r="H359" t="n">
-        <v>1.9</v>
+        <v>17.09</v>
       </c>
       <c r="I359" t="n">
-        <v>34.89</v>
+        <v>816.5599999999999</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
@@ -36666,37 +36683,37 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>00.01</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>VENITURILE SECTIUNII DE FUNCTIONARE - TOTAL</t>
+          <t>AUTORITATI PUBLICE SI ACTIUNI</t>
         </is>
       </c>
       <c r="G360" t="n">
-        <v>125923.7</v>
+        <v>36414.73</v>
       </c>
       <c r="H360" t="n">
-        <v>34.46</v>
+        <v>14.35</v>
       </c>
       <c r="I360" t="n">
-        <v>3651.66</v>
+        <v>685.61</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -36710,37 +36727,37 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>00.03</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>A. VENITURI FISCALE</t>
+          <t>INVATAMANT</t>
         </is>
       </c>
       <c r="G361" t="n">
-        <v>121046</v>
+        <v>34979.21</v>
       </c>
       <c r="H361" t="n">
-        <v>33.13</v>
+        <v>13.78</v>
       </c>
       <c r="I361" t="n">
-        <v>3510.21</v>
+        <v>658.58</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36754,37 +36771,37 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>00.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>I. VENITURI CURENTE</t>
+          <t>PROTECTIA MEDIULUI</t>
         </is>
       </c>
       <c r="G362" t="n">
-        <v>120769</v>
+        <v>14796.73</v>
       </c>
       <c r="H362" t="n">
-        <v>33.05</v>
+        <v>5.83</v>
       </c>
       <c r="I362" t="n">
-        <v>3502.17</v>
+        <v>278.59</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -36798,37 +36815,37 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>00.04</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>A1. IMPOZIT PE VENIT, PROFIT SI CASTIGURI DIN CAPITAL</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>69144</v>
+        <v>12183.34</v>
       </c>
       <c r="H363" t="n">
-        <v>18.92</v>
+        <v>4.8</v>
       </c>
       <c r="I363" t="n">
-        <v>2005.1</v>
+        <v>229.39</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -36842,37 +36859,37 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>00.06</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>A1.2. IMPOZIT PE VENIT, PROFIT, SI CASTIGURI DIN CAPITAL DE LA PERSOAN</t>
+          <t>Ordine publica si siguranta natierala</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>69144</v>
+        <v>10964.9</v>
       </c>
       <c r="H364" t="n">
-        <v>18.92</v>
+        <v>4.32</v>
       </c>
       <c r="I364" t="n">
-        <v>2005.1</v>
+        <v>206.44</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -36886,37 +36903,37 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Deva</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Hunedoara</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>00.10</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>A4. IMPOZITE SI TAXE PE BUNURI SI SERVICII</t>
+          <t>TRANZACTII PRIVIND DATORIA PUBLICA IMPRUMUTURI</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>36792</v>
+        <v>6214</v>
       </c>
       <c r="H365" t="n">
-        <v>10.07</v>
+        <v>2.45</v>
       </c>
       <c r="I365" t="n">
-        <v>1066.93</v>
+        <v>117</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -36930,37 +36947,37 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Slobozia</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>00.09</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>A3. IMPOZITE SI TAXE PE PROPRIETATE</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>14670</v>
+        <v>47507.935</v>
       </c>
       <c r="H366" t="n">
-        <v>4.01</v>
+        <v>20.09</v>
       </c>
       <c r="I366" t="n">
-        <v>425.41</v>
+        <v>1143.39</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -36974,37 +36991,37 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Slobozia</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>12170.2</v>
+        <v>37068.963</v>
       </c>
       <c r="H367" t="n">
-        <v>3.33</v>
+        <v>15.67</v>
       </c>
       <c r="I367" t="n">
-        <v>352.92</v>
+        <v>892.15</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -37018,37 +37035,37 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Slobozia</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Combustibili si energie</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>5311</v>
+        <v>32137.5</v>
       </c>
       <c r="H368" t="n">
-        <v>1.45</v>
+        <v>13.59</v>
       </c>
       <c r="I368" t="n">
-        <v>154.01</v>
+        <v>773.47</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
@@ -37062,37 +37079,37 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>92658</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Miercurea Ciuc</t>
+          <t>Slobozia</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Harghita</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare:publica</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>5125.5</v>
+        <v>27926.999</v>
       </c>
       <c r="H369" t="n">
-        <v>1.4</v>
+        <v>11.81</v>
       </c>
       <c r="I369" t="n">
-        <v>148.63</v>
+        <v>672.13</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
@@ -37121,22 +37138,22 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G370" t="n">
-        <v>47507.935</v>
+        <v>27499.259</v>
       </c>
       <c r="H370" t="n">
-        <v>20.09</v>
+        <v>11.63</v>
       </c>
       <c r="I370" t="n">
-        <v>1143.39</v>
+        <v>661.84</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
@@ -37165,22 +37182,22 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>37068.963</v>
+        <v>25714.346</v>
       </c>
       <c r="H371" t="n">
-        <v>15.67</v>
+        <v>10.87</v>
       </c>
       <c r="I371" t="n">
-        <v>892.15</v>
+        <v>618.88</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
@@ -37209,22 +37226,22 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G372" t="n">
-        <v>32137.5</v>
+        <v>20609.528</v>
       </c>
       <c r="H372" t="n">
-        <v>13.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I372" t="n">
-        <v>773.47</v>
+        <v>496.02</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
@@ -37253,22 +37270,22 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G373" t="n">
-        <v>27926.999</v>
+        <v>7849.833</v>
       </c>
       <c r="H373" t="n">
-        <v>11.81</v>
+        <v>3.32</v>
       </c>
       <c r="I373" t="n">
-        <v>672.13</v>
+        <v>188.92</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -37297,22 +37314,22 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G374" t="n">
-        <v>27499.259</v>
+        <v>3580.364</v>
       </c>
       <c r="H374" t="n">
-        <v>11.63</v>
+        <v>1.51</v>
       </c>
       <c r="I374" t="n">
-        <v>661.84</v>
+        <v>86.17</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
@@ -37341,22 +37358,22 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G375" t="n">
-        <v>25714.346</v>
+        <v>3016</v>
       </c>
       <c r="H375" t="n">
-        <v>10.87</v>
+        <v>1.28</v>
       </c>
       <c r="I375" t="n">
-        <v>618.88</v>
+        <v>72.59</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
@@ -37370,37 +37387,37 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Slobozia</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Ialomița</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G376" t="n">
-        <v>20609.528</v>
+        <v>44457.9</v>
       </c>
       <c r="H376" t="n">
-        <v>8.710000000000001</v>
+        <v>2.54</v>
       </c>
       <c r="I376" t="n">
-        <v>496.02</v>
+        <v>163.63</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
@@ -37414,37 +37431,37 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Slobozia</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Ialomița</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G377" t="n">
-        <v>7849.833</v>
+        <v>38987.05</v>
       </c>
       <c r="H377" t="n">
-        <v>3.32</v>
+        <v>2.23</v>
       </c>
       <c r="I377" t="n">
-        <v>188.92</v>
+        <v>143.5</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -37458,37 +37475,37 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Slobozia</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Ialomița</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G378" t="n">
-        <v>3580.364</v>
+        <v>35671</v>
       </c>
       <c r="H378" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="I378" t="n">
-        <v>86.17</v>
+        <v>131.29</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -37502,37 +37519,37 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>92658</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Slobozia</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Ialomița</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Alte actiuni economice</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>3016</v>
+        <v>14270</v>
       </c>
       <c r="H379" t="n">
-        <v>1.28</v>
+        <v>0.82</v>
       </c>
       <c r="I379" t="n">
-        <v>72.59</v>
+        <v>52.52</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
@@ -37546,37 +37563,37 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>106318</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Baia Mare</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Maramureș</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>159420</v>
+        <v>455.07</v>
       </c>
       <c r="H380" t="n">
-        <v>20.11</v>
+        <v>0.03</v>
       </c>
       <c r="I380" t="n">
-        <v>1465.81</v>
+        <v>1.67</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
@@ -37590,37 +37607,37 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>106318</t>
+          <t>95060</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Baia Mare</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Maramureș</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>66.10</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>69804</v>
+        <v>0</v>
       </c>
       <c r="H381" t="n">
-        <v>8.81</v>
+        <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>641.8200000000001</v>
+        <v>0</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -37649,22 +37666,22 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>00.10</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>A4. IMPOZITE SI TAXE PE BUNURI SI SERVICII</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>67756</v>
+        <v>159420</v>
       </c>
       <c r="H382" t="n">
-        <v>8.550000000000001</v>
+        <v>20.11</v>
       </c>
       <c r="I382" t="n">
-        <v>622.99</v>
+        <v>1465.81</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -37693,22 +37710,22 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>00.12</t>
+          <t>66.10</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>C. VENITURI NEFISCALE</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>39353</v>
+        <v>69804</v>
       </c>
       <c r="H383" t="n">
-        <v>4.97</v>
+        <v>8.81</v>
       </c>
       <c r="I383" t="n">
-        <v>361.84</v>
+        <v>641.8200000000001</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -37737,22 +37754,22 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>70.10</t>
+          <t>00.10</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>A4. IMPOZITE SI TAXE PE BUNURI SI SERVICII</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>29620</v>
+        <v>67756</v>
       </c>
       <c r="H384" t="n">
-        <v>3.74</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I384" t="n">
-        <v>272.35</v>
+        <v>622.99</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
@@ -37781,22 +37798,22 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>00.14</t>
+          <t>00.12</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>C2. VANZARI DE BUNURI SI SERVICII</t>
+          <t>C. VENITURI NEFISCALE</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>26524</v>
+        <v>39353</v>
       </c>
       <c r="H385" t="n">
-        <v>3.35</v>
+        <v>4.97</v>
       </c>
       <c r="I385" t="n">
-        <v>243.88</v>
+        <v>361.84</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
@@ -37825,22 +37842,22 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>67.10</t>
+          <t>70.10</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie (67.10.03+67.10.05+67.10.50)</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G386" t="n">
-        <v>19424</v>
+        <v>29620</v>
       </c>
       <c r="H386" t="n">
-        <v>2.45</v>
+        <v>3.74</v>
       </c>
       <c r="I386" t="n">
-        <v>178.6</v>
+        <v>272.35</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
@@ -37869,22 +37886,22 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>00.13</t>
+          <t>00.14</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>C1. VENITURI DIN PROPRIETATE</t>
+          <t>C2. VANZARI DE BUNURI SI SERVICII</t>
         </is>
       </c>
       <c r="G387" t="n">
-        <v>12829</v>
+        <v>26524</v>
       </c>
       <c r="H387" t="n">
-        <v>1.62</v>
+        <v>3.35</v>
       </c>
       <c r="I387" t="n">
-        <v>117.96</v>
+        <v>243.88</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
@@ -37913,22 +37930,22 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>67.10</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Cultura, recreere si religie (67.10.03+67.10.05+67.10.50)</t>
         </is>
       </c>
       <c r="G388" t="n">
-        <v>10494.5</v>
+        <v>19424</v>
       </c>
       <c r="H388" t="n">
-        <v>1.32</v>
+        <v>2.45</v>
       </c>
       <c r="I388" t="n">
-        <v>96.48999999999999</v>
+        <v>178.6</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -37957,22 +37974,22 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>65.10</t>
+          <t>00.13</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>C1. VENITURI DIN PROPRIETATE</t>
         </is>
       </c>
       <c r="G389" t="n">
-        <v>9875</v>
+        <v>12829</v>
       </c>
       <c r="H389" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="I389" t="n">
-        <v>90.8</v>
+        <v>117.96</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
@@ -37986,37 +38003,37 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>120726</t>
+          <t>106318</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Piatra-Neamț</t>
+          <t>Baia Mare</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Neamț</t>
+          <t>Maramureș</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe Din total capitol:</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G390" t="n">
-        <v>68075.99000000001</v>
+        <v>10494.5</v>
       </c>
       <c r="H390" t="n">
-        <v>12.29</v>
+        <v>1.32</v>
       </c>
       <c r="I390" t="n">
-        <v>854.38</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
@@ -38030,37 +38047,37 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>120726</t>
+          <t>106318</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Piatra-Neamț</t>
+          <t>Baia Mare</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Neamț</t>
+          <t>Maramureș</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>65.10</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie Din total capitol:</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G391" t="n">
-        <v>35552.68</v>
+        <v>9875</v>
       </c>
       <c r="H391" t="n">
-        <v>6.42</v>
+        <v>1.25</v>
       </c>
       <c r="I391" t="n">
-        <v>446.2</v>
+        <v>90.8</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
@@ -38089,22 +38106,22 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Protectia mediului Din total capitol:</t>
+          <t>Autoritati publice si actiuni externe Din total capitol:</t>
         </is>
       </c>
       <c r="G392" t="n">
-        <v>12023</v>
+        <v>68075.99000000001</v>
       </c>
       <c r="H392" t="n">
-        <v>2.17</v>
+        <v>12.29</v>
       </c>
       <c r="I392" t="n">
-        <v>150.89</v>
+        <v>854.38</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
@@ -38133,22 +38150,22 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>Tranzacții privind datoria publică şi imprumuturi</t>
+          <t>Cultura, recreere si religie Din total capitol:</t>
         </is>
       </c>
       <c r="G393" t="n">
-        <v>7885</v>
+        <v>35552.68</v>
       </c>
       <c r="H393" t="n">
-        <v>1.42</v>
+        <v>6.42</v>
       </c>
       <c r="I393" t="n">
-        <v>98.95999999999999</v>
+        <v>446.2</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -38177,22 +38194,22 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Sanatate Din total capitol:</t>
+          <t>Tranzacții privind datoria publică şi imprumuturi</t>
         </is>
       </c>
       <c r="G394" t="n">
-        <v>5958</v>
+        <v>7885</v>
       </c>
       <c r="H394" t="n">
-        <v>1.08</v>
+        <v>1.42</v>
       </c>
       <c r="I394" t="n">
-        <v>74.78</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -38221,22 +38238,22 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>54.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Alte servicii publice generale</t>
+          <t>Sanatate Din total capitol:</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>350</v>
+        <v>5958</v>
       </c>
       <c r="H395" t="n">
-        <v>0.06</v>
+        <v>1.08</v>
       </c>
       <c r="I395" t="n">
-        <v>4.39</v>
+        <v>74.78</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
@@ -38274,13 +38291,13 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H396" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I396" t="n">
-        <v>0</v>
+        <v>17.57</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
@@ -38294,37 +38311,37 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>136483</t>
+          <t>120726</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Satu Mare</t>
+          <t>Piatra-Neamț</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Satu Mare</t>
+          <t>Neamț</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G397" t="n">
-        <v>138203.457</v>
+        <v>350</v>
       </c>
       <c r="H397" t="n">
-        <v>23.91</v>
+        <v>0.06</v>
       </c>
       <c r="I397" t="n">
-        <v>1510.09</v>
+        <v>4.39</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -38353,22 +38370,22 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G398" t="n">
-        <v>120718.976</v>
+        <v>138203.457</v>
       </c>
       <c r="H398" t="n">
-        <v>20.89</v>
+        <v>23.91</v>
       </c>
       <c r="I398" t="n">
-        <v>1319.04</v>
+        <v>1510.09</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
@@ -38397,22 +38414,22 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>106680.741</v>
+        <v>120718.976</v>
       </c>
       <c r="H399" t="n">
-        <v>18.46</v>
+        <v>20.89</v>
       </c>
       <c r="I399" t="n">
-        <v>1165.65</v>
+        <v>1319.04</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
@@ -38441,22 +38458,22 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G400" t="n">
-        <v>70038.5</v>
+        <v>106680.741</v>
       </c>
       <c r="H400" t="n">
-        <v>12.12</v>
+        <v>18.46</v>
       </c>
       <c r="I400" t="n">
-        <v>765.28</v>
+        <v>1165.65</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -38485,22 +38502,22 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G401" t="n">
-        <v>61026.02</v>
+        <v>70038.5</v>
       </c>
       <c r="H401" t="n">
-        <v>10.56</v>
+        <v>12.12</v>
       </c>
       <c r="I401" t="n">
-        <v>666.8099999999999</v>
+        <v>765.28</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
@@ -38529,22 +38546,22 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G402" t="n">
-        <v>42532</v>
+        <v>61026.02</v>
       </c>
       <c r="H402" t="n">
-        <v>7.36</v>
+        <v>10.56</v>
       </c>
       <c r="I402" t="n">
-        <v>464.73</v>
+        <v>666.8099999999999</v>
       </c>
       <c r="J402" t="inlineStr">
         <is>
@@ -38573,22 +38590,22 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G403" t="n">
-        <v>14216.4</v>
+        <v>42532</v>
       </c>
       <c r="H403" t="n">
-        <v>2.46</v>
+        <v>7.36</v>
       </c>
       <c r="I403" t="n">
-        <v>155.34</v>
+        <v>464.73</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -38617,22 +38634,22 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G404" t="n">
-        <v>8355</v>
+        <v>14216.4</v>
       </c>
       <c r="H404" t="n">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="I404" t="n">
-        <v>91.29000000000001</v>
+        <v>155.34</v>
       </c>
       <c r="J404" t="inlineStr">
         <is>
@@ -38661,22 +38678,22 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G405" t="n">
-        <v>7468.1</v>
+        <v>8355</v>
       </c>
       <c r="H405" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="I405" t="n">
-        <v>81.59999999999999</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="J405" t="inlineStr">
         <is>
@@ -38705,22 +38722,22 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>Tranzacţii privind datoria publică şi împrumuturi</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G406" t="n">
-        <v>4442</v>
+        <v>7468.1</v>
       </c>
       <c r="H406" t="n">
-        <v>0.77</v>
+        <v>1.29</v>
       </c>
       <c r="I406" t="n">
-        <v>48.54</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="J406" t="inlineStr">
         <is>
@@ -38734,37 +38751,37 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Satu Mare</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Satu Mare</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
+          <t>Tranzacţii privind datoria publică şi împrumuturi</t>
         </is>
       </c>
       <c r="G407" t="n">
-        <v>155554.72</v>
+        <v>4442</v>
       </c>
       <c r="H407" t="n">
-        <v>35.65</v>
+        <v>0.77</v>
       </c>
       <c r="I407" t="n">
-        <v>3851.32</v>
+        <v>48.54</v>
       </c>
       <c r="J407" t="inlineStr">
         <is>
@@ -38778,37 +38795,37 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>TRANSPORTURI</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G408" t="n">
-        <v>126153.18</v>
+        <v>72189310</v>
       </c>
       <c r="H408" t="n">
-        <v>28.91</v>
+        <v>6748.3</v>
       </c>
       <c r="I408" t="n">
-        <v>3123.38</v>
+        <v>856114.77</v>
       </c>
       <c r="J408" t="inlineStr">
         <is>
@@ -38822,37 +38839,37 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>INVATAMANT</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G409" t="n">
-        <v>59801.17</v>
+        <v>47770840</v>
       </c>
       <c r="H409" t="n">
-        <v>13.7</v>
+        <v>4465.65</v>
       </c>
       <c r="I409" t="n">
-        <v>1480.59</v>
+        <v>566528.78</v>
       </c>
       <c r="J409" t="inlineStr">
         <is>
@@ -38866,37 +38883,37 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G410" t="n">
-        <v>27535.95</v>
+        <v>39480560</v>
       </c>
       <c r="H410" t="n">
-        <v>6.31</v>
+        <v>3690.67</v>
       </c>
       <c r="I410" t="n">
-        <v>681.75</v>
+        <v>468211.85</v>
       </c>
       <c r="J410" t="inlineStr">
         <is>
@@ -38910,37 +38927,37 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>CULTURA, RECREERE SI RELIGIE</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G411" t="n">
-        <v>22298.25</v>
+        <v>37260960</v>
       </c>
       <c r="H411" t="n">
-        <v>5.11</v>
+        <v>3483.18</v>
       </c>
       <c r="I411" t="n">
-        <v>552.0700000000001</v>
+        <v>441888.95</v>
       </c>
       <c r="J411" t="inlineStr">
         <is>
@@ -38954,37 +38971,37 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>80.02</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
+          <t>Actiuni generale economice, comerciale si de munca</t>
         </is>
       </c>
       <c r="G412" t="n">
-        <v>20779.28</v>
+        <v>30324290</v>
       </c>
       <c r="H412" t="n">
-        <v>4.76</v>
+        <v>2834.73</v>
       </c>
       <c r="I412" t="n">
-        <v>514.47</v>
+        <v>359624.89</v>
       </c>
       <c r="J412" t="inlineStr">
         <is>
@@ -38998,37 +39015,37 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PROTECTIA MEDIULUI</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>9990</v>
+        <v>16022160</v>
       </c>
       <c r="H413" t="n">
-        <v>2.29</v>
+        <v>1497.76</v>
       </c>
       <c r="I413" t="n">
-        <v>247.34</v>
+        <v>190011.62</v>
       </c>
       <c r="J413" t="inlineStr">
         <is>
@@ -39042,37 +39059,37 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>55.02</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SANATATE</t>
+          <t>Tranzactii privind datoria publica si imprumuturi</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>5656.95</v>
+        <v>9082500</v>
       </c>
       <c r="H414" t="n">
-        <v>1.3</v>
+        <v>849.04</v>
       </c>
       <c r="I414" t="n">
-        <v>140.06</v>
+        <v>107712.1</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -39086,37 +39103,37 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G415" t="n">
-        <v>4304.54</v>
+        <v>8153970</v>
       </c>
       <c r="H415" t="n">
-        <v>0.99</v>
+        <v>762.24</v>
       </c>
       <c r="I415" t="n">
-        <v>106.57</v>
+        <v>96700.39</v>
       </c>
       <c r="J415" t="inlineStr">
         <is>
@@ -39130,17 +39147,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>151790</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -39150,17 +39167,17 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>ALTE SERVICII PUBLICE GENERALE</t>
+          <t>Alte servicii publice generale</t>
         </is>
       </c>
       <c r="G416" t="n">
-        <v>2236.86</v>
+        <v>6885390</v>
       </c>
       <c r="H416" t="n">
-        <v>0.51</v>
+        <v>643.65</v>
       </c>
       <c r="I416" t="n">
-        <v>55.38</v>
+        <v>81655.91</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -39174,37 +39191,37 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Alte actiuni economice</t>
         </is>
       </c>
       <c r="G417" t="n">
-        <v>686977.25</v>
+        <v>493480</v>
       </c>
       <c r="H417" t="n">
-        <v>29.2</v>
+        <v>46.13</v>
       </c>
       <c r="I417" t="n">
-        <v>2738.61</v>
+        <v>5852.33</v>
       </c>
       <c r="J417" t="inlineStr">
         <is>
@@ -39218,37 +39235,37 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Invatamant</t>
+          <t>LOCUINTE, SERVICII SI DEZVOLTARE</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>373107.36</v>
+        <v>155554.72</v>
       </c>
       <c r="H418" t="n">
-        <v>15.86</v>
+        <v>35.65</v>
       </c>
       <c r="I418" t="n">
-        <v>1487.38</v>
+        <v>3851.32</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -39262,37 +39279,37 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>TRANSPORTURI</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>301999.69</v>
+        <v>126153.18</v>
       </c>
       <c r="H419" t="n">
-        <v>12.84</v>
+        <v>28.91</v>
       </c>
       <c r="I419" t="n">
-        <v>1203.91</v>
+        <v>3123.38</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -39306,37 +39323,37 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>INVATAMANT</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>207691.08</v>
+        <v>59801.17</v>
       </c>
       <c r="H420" t="n">
-        <v>8.83</v>
+        <v>13.7</v>
       </c>
       <c r="I420" t="n">
-        <v>827.95</v>
+        <v>1480.59</v>
       </c>
       <c r="J420" t="inlineStr">
         <is>
@@ -39350,17 +39367,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -39370,17 +39387,17 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>ASIGURARI SI ASISTENTA SOCIALA</t>
         </is>
       </c>
       <c r="G421" t="n">
-        <v>194524.94</v>
+        <v>27535.95</v>
       </c>
       <c r="H421" t="n">
-        <v>8.27</v>
+        <v>6.31</v>
       </c>
       <c r="I421" t="n">
-        <v>775.47</v>
+        <v>681.75</v>
       </c>
       <c r="J421" t="inlineStr">
         <is>
@@ -39394,37 +39411,37 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>81.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>Combustibili si energie</t>
+          <t>CULTURA, RECREERE SI RELIGIE</t>
         </is>
       </c>
       <c r="G422" t="n">
-        <v>153215.51</v>
+        <v>22298.25</v>
       </c>
       <c r="H422" t="n">
-        <v>6.51</v>
+        <v>5.11</v>
       </c>
       <c r="I422" t="n">
-        <v>610.79</v>
+        <v>552.0700000000001</v>
       </c>
       <c r="J422" t="inlineStr">
         <is>
@@ -39438,17 +39455,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -39458,17 +39475,17 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>AUTORITATI PUBLICE SI ACTIUNI EXTERNE</t>
         </is>
       </c>
       <c r="G423" t="n">
-        <v>143332.88</v>
+        <v>20779.28</v>
       </c>
       <c r="H423" t="n">
-        <v>6.09</v>
+        <v>4.76</v>
       </c>
       <c r="I423" t="n">
-        <v>571.39</v>
+        <v>514.47</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -39482,17 +39499,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -39502,17 +39519,17 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>PROTECTIA MEDIULUI</t>
         </is>
       </c>
       <c r="G424" t="n">
-        <v>124598.15</v>
+        <v>9990</v>
       </c>
       <c r="H424" t="n">
-        <v>5.3</v>
+        <v>2.29</v>
       </c>
       <c r="I424" t="n">
-        <v>496.71</v>
+        <v>247.34</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -39526,17 +39543,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -39546,17 +39563,17 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>SANATATE</t>
         </is>
       </c>
       <c r="G425" t="n">
-        <v>87888.77</v>
+        <v>5656.95</v>
       </c>
       <c r="H425" t="n">
-        <v>3.74</v>
+        <v>1.3</v>
       </c>
       <c r="I425" t="n">
-        <v>350.37</v>
+        <v>140.06</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -39570,17 +39587,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>155243</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Timișoara</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Timiș</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -39590,17 +39607,17 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>ORDINE PUBLICA SI SIGURANTA NATIONALA</t>
         </is>
       </c>
       <c r="G426" t="n">
-        <v>50093.81</v>
+        <v>4304.54</v>
       </c>
       <c r="H426" t="n">
-        <v>2.13</v>
+        <v>0.99</v>
       </c>
       <c r="I426" t="n">
-        <v>199.7</v>
+        <v>106.57</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -39614,37 +39631,37 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>151790</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>54.02</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>Asigurari si asistenta sociala</t>
+          <t>ALTE SERVICII PUBLICE GENERALE</t>
         </is>
       </c>
       <c r="G427" t="n">
-        <v>33318</v>
+        <v>2236.86</v>
       </c>
       <c r="H427" t="n">
-        <v>12.9</v>
+        <v>0.51</v>
       </c>
       <c r="I427" t="n">
-        <v>507.71</v>
+        <v>55.38</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -39658,37 +39675,37 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>Autoritati publice si actiuni externe</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G428" t="n">
-        <v>32233.8</v>
+        <v>686977.25</v>
       </c>
       <c r="H428" t="n">
-        <v>12.48</v>
+        <v>29.2</v>
       </c>
       <c r="I428" t="n">
-        <v>491.19</v>
+        <v>2738.61</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -39702,17 +39719,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -39726,13 +39743,13 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>24022.1</v>
+        <v>373107.36</v>
       </c>
       <c r="H429" t="n">
-        <v>9.300000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="I429" t="n">
-        <v>366.06</v>
+        <v>1487.38</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -39746,37 +39763,37 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>Locuinte, servicii si dezvoltare publica</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G430" t="n">
-        <v>20474</v>
+        <v>301999.69</v>
       </c>
       <c r="H430" t="n">
-        <v>7.92</v>
+        <v>12.84</v>
       </c>
       <c r="I430" t="n">
-        <v>311.99</v>
+        <v>1203.91</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -39790,37 +39807,37 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Transporturi</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G431" t="n">
-        <v>17025</v>
+        <v>207691.08</v>
       </c>
       <c r="H431" t="n">
-        <v>6.59</v>
+        <v>8.83</v>
       </c>
       <c r="I431" t="n">
-        <v>259.43</v>
+        <v>827.95</v>
       </c>
       <c r="J431" t="inlineStr">
         <is>
@@ -39834,37 +39851,37 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>Cultura, recreere si religie</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G432" t="n">
-        <v>15266</v>
+        <v>194524.94</v>
       </c>
       <c r="H432" t="n">
-        <v>5.91</v>
+        <v>8.27</v>
       </c>
       <c r="I432" t="n">
-        <v>232.63</v>
+        <v>775.47</v>
       </c>
       <c r="J432" t="inlineStr">
         <is>
@@ -39878,37 +39895,37 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>81.02</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>Protectia mediului</t>
+          <t>Combustibili si energie</t>
         </is>
       </c>
       <c r="G433" t="n">
-        <v>12534.6</v>
+        <v>153215.51</v>
       </c>
       <c r="H433" t="n">
-        <v>4.85</v>
+        <v>6.51</v>
       </c>
       <c r="I433" t="n">
-        <v>191.01</v>
+        <v>610.79</v>
       </c>
       <c r="J433" t="inlineStr">
         <is>
@@ -39922,37 +39939,37 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>Ordine publica si siguranta nationala</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G434" t="n">
-        <v>10148</v>
+        <v>143332.88</v>
       </c>
       <c r="H434" t="n">
-        <v>3.93</v>
+        <v>6.09</v>
       </c>
       <c r="I434" t="n">
-        <v>154.64</v>
+        <v>571.39</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
@@ -39966,37 +39983,37 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>66.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>Sanatate</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G435" t="n">
-        <v>6402.6</v>
+        <v>124598.15</v>
       </c>
       <c r="H435" t="n">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="I435" t="n">
-        <v>97.56</v>
+        <v>496.71</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
@@ -40010,37 +40027,37 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>159614</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Tulcea</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>66.02</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>Alte actiuni economice</t>
+          <t>Sanatate</t>
         </is>
       </c>
       <c r="G436" t="n">
-        <v>6100</v>
+        <v>87888.77</v>
       </c>
       <c r="H436" t="n">
-        <v>2.36</v>
+        <v>3.74</v>
       </c>
       <c r="I436" t="n">
-        <v>92.95</v>
+        <v>350.37</v>
       </c>
       <c r="J436" t="inlineStr">
         <is>
@@ -40054,37 +40071,37 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>155243</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Timișoara</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Timiș</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>61.02</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>Transporturi - din care titlurile:</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G437" t="n">
-        <v>194801000</v>
+        <v>50093.81</v>
       </c>
       <c r="H437" t="n">
-        <v>39468.31</v>
+        <v>2.13</v>
       </c>
       <c r="I437" t="n">
-        <v>3090362.5</v>
+        <v>199.7</v>
       </c>
       <c r="J437" t="inlineStr">
         <is>
@@ -40098,37 +40115,37 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>Locuințe, servicii și dezvoltare publică - din care titlurile:</t>
+          <t>Asigurari si asistenta sociala</t>
         </is>
       </c>
       <c r="G438" t="n">
-        <v>63247080</v>
+        <v>33318</v>
       </c>
       <c r="H438" t="n">
-        <v>12814.39</v>
+        <v>12.9</v>
       </c>
       <c r="I438" t="n">
-        <v>1003364.48</v>
+        <v>507.71</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -40142,37 +40159,37 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>65.02</t>
+          <t>51.02</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>Învățământ - din care titlurile:</t>
+          <t>Autoritati publice si actiuni externe</t>
         </is>
       </c>
       <c r="G439" t="n">
-        <v>61247000</v>
+        <v>32233.8</v>
       </c>
       <c r="H439" t="n">
-        <v>12409.15</v>
+        <v>12.48</v>
       </c>
       <c r="I439" t="n">
-        <v>971634.8100000001</v>
+        <v>491.19</v>
       </c>
       <c r="J439" t="inlineStr">
         <is>
@@ -40186,37 +40203,37 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>Asigurări și asistență socială - din care titlurile:</t>
+          <t>Invatamant</t>
         </is>
       </c>
       <c r="G440" t="n">
-        <v>48726000</v>
+        <v>24022.1</v>
       </c>
       <c r="H440" t="n">
-        <v>9872.290000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I440" t="n">
-        <v>772999.13</v>
+        <v>366.06</v>
       </c>
       <c r="J440" t="inlineStr">
         <is>
@@ -40230,37 +40247,37 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>Autorități publice și acțiuni externe - din care titlurile:</t>
+          <t>Locuinte, servicii si dezvoltare publica</t>
         </is>
       </c>
       <c r="G441" t="n">
-        <v>37385000</v>
+        <v>20474</v>
       </c>
       <c r="H441" t="n">
-        <v>7574.51</v>
+        <v>7.92</v>
       </c>
       <c r="I441" t="n">
-        <v>593083.21</v>
+        <v>311.99</v>
       </c>
       <c r="J441" t="inlineStr">
         <is>
@@ -40274,37 +40291,37 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>74.02</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>Protecția mediului - din care titlurile:</t>
+          <t>Transporturi</t>
         </is>
       </c>
       <c r="G442" t="n">
-        <v>33338000</v>
+        <v>17025</v>
       </c>
       <c r="H442" t="n">
-        <v>6754.56</v>
+        <v>6.59</v>
       </c>
       <c r="I442" t="n">
-        <v>528880.78</v>
+        <v>259.43</v>
       </c>
       <c r="J442" t="inlineStr">
         <is>
@@ -40318,37 +40335,37 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>00.01</t>
+          <t>67.02</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>VENITURILE SECTIUNII DE FUNCTIONARE</t>
+          <t>Cultura, recreere si religie</t>
         </is>
       </c>
       <c r="G443" t="n">
-        <v>32001000</v>
+        <v>15266</v>
       </c>
       <c r="H443" t="n">
-        <v>6483.67</v>
+        <v>5.91</v>
       </c>
       <c r="I443" t="n">
-        <v>507670.34</v>
+        <v>232.63</v>
       </c>
       <c r="J443" t="inlineStr">
         <is>
@@ -40362,37 +40379,37 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>67.02</t>
+          <t>74.02</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>Cultură, recreere și religie - din care titlurile:</t>
+          <t>Protectia mediului</t>
         </is>
       </c>
       <c r="G444" t="n">
-        <v>31728000</v>
+        <v>12534.6</v>
       </c>
       <c r="H444" t="n">
-        <v>6428.36</v>
+        <v>4.85</v>
       </c>
       <c r="I444" t="n">
-        <v>503339.41</v>
+        <v>191.01</v>
       </c>
       <c r="J444" t="inlineStr">
         <is>
@@ -40406,17 +40423,17 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>161945</t>
+          <t>159614</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Tulcea</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -40426,17 +40443,17 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>Ordine publică și siguranță națională - din care titlurile:</t>
+          <t>Ordine publica si siguranta nationala</t>
         </is>
       </c>
       <c r="G445" t="n">
-        <v>14333000</v>
+        <v>10148</v>
       </c>
       <c r="H445" t="n">
-        <v>2903.99</v>
+        <v>3.93</v>
       </c>
       <c r="I445" t="n">
-        <v>227381.61</v>
+        <v>154.64</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
@@ -40450,46 +40467,530 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
+          <t>159614</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Tulcea</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Tulcea</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>66.02</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Sanatate</t>
+        </is>
+      </c>
+      <c r="G446" t="n">
+        <v>6402.6</v>
+      </c>
+      <c r="H446" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I446" t="n">
+        <v>97.56</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>159614</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Tulcea</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Tulcea</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Alte actiuni economice</t>
+        </is>
+      </c>
+      <c r="G447" t="n">
+        <v>6100</v>
+      </c>
+      <c r="H447" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I447" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
           <t>161945</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>Vaslui</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
+      <c r="D448" t="inlineStr">
         <is>
           <t>Vaslui</t>
         </is>
       </c>
-      <c r="E446" t="inlineStr">
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>84.02</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Transporturi - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G448" t="n">
+        <v>194801000</v>
+      </c>
+      <c r="H448" t="n">
+        <v>39468.31</v>
+      </c>
+      <c r="I448" t="n">
+        <v>3090362.5</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>70.02</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Locuințe, servicii și dezvoltare publică - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>63247080</v>
+      </c>
+      <c r="H449" t="n">
+        <v>12814.39</v>
+      </c>
+      <c r="I449" t="n">
+        <v>1003364.48</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>65.02</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Învățământ - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>61247000</v>
+      </c>
+      <c r="H450" t="n">
+        <v>12409.15</v>
+      </c>
+      <c r="I450" t="n">
+        <v>971634.8100000001</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>68.02</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Asigurări și asistență socială - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>48726000</v>
+      </c>
+      <c r="H451" t="n">
+        <v>9872.290000000001</v>
+      </c>
+      <c r="I451" t="n">
+        <v>772999.13</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>51.02</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Autorități publice și acțiuni externe - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>37385000</v>
+      </c>
+      <c r="H452" t="n">
+        <v>7574.51</v>
+      </c>
+      <c r="I452" t="n">
+        <v>593083.21</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Protecția mediului - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>33338000</v>
+      </c>
+      <c r="H453" t="n">
+        <v>6754.56</v>
+      </c>
+      <c r="I453" t="n">
+        <v>528880.78</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>67.02</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Cultură, recreere și religie - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>31728000</v>
+      </c>
+      <c r="H454" t="n">
+        <v>6428.36</v>
+      </c>
+      <c r="I454" t="n">
+        <v>503339.41</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>61.02</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Ordine publică și siguranță națională - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>14333000</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2903.99</v>
+      </c>
+      <c r="I455" t="n">
+        <v>227381.61</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
         <is>
           <t>61.10</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr">
+      <c r="F456" t="inlineStr">
         <is>
           <t>Ordine publică și siguranță națională - din care titlurile:</t>
         </is>
       </c>
-      <c r="G446" t="n">
+      <c r="G456" t="n">
         <v>13675000</v>
       </c>
-      <c r="H446" t="n">
+      <c r="H456" t="n">
         <v>2770.67</v>
       </c>
-      <c r="I446" t="n">
+      <c r="I456" t="n">
         <v>216942.97</v>
       </c>
-      <c r="J446" t="inlineStr">
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>161945</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>67.10</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Cultură, recreere și religie - din care titlurile:</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>9394000</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1903.3</v>
+      </c>
+      <c r="I457" t="n">
+        <v>149028.32</v>
+      </c>
+      <c r="J457" t="inlineStr">
         <is>
           <t>Capitol prezent în topul verificat al municipiului; lista nu este exhaustivă.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J446"/>
+  <autoFilter ref="A1:J457"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
